--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28077-2024 artfynd.xlsx
+++ b/artfynd/A 28077-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929216</v>
       </c>
       <c r="B2" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136929217</v>
       </c>
       <c r="B3" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
